--- a/高等教育学2026.xlsx
+++ b/高等教育学2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B459"/>
+  <dimension ref="A1:B449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,23 +1950,6 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>00091_单选题
-（     ）是现代高等学校的根本使命。（该题目已移除！）
-A.培养专门人才；
-B.发展科学；
-C.服务社会；
-D.国际合作；</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
           <t>00092_单选题
 对自己所从事专业的目标、文化以及专业共同体从心理上认同并且树立起坚定的专业信念、专业责任和专业荣誉感，是指（     ）。
 A.专业知识；
@@ -1975,14 +1958,14 @@
 D.专业人格；</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>00093_单选题
 评价教师在课堂教学中对学生运用知识、形成能力的重视情况，属于教学评价中的（     ）方面评价。
@@ -1992,14 +1975,14 @@
 D.习惯；</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>00094_单选题
 大学生学业成绩考核的原则是（     ）。
@@ -2009,14 +1992,14 @@
 D.科学性原则、激励性原则。；</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>00095_单选题
 完整的高等教育体系首先在（     ）形成，继而影响了整个西方世界。
@@ -2026,14 +2009,14 @@
 D.法国；</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>00096_单选题
 （     ）是高校学科建设的核心内容，直接决定教学的成败。
@@ -2043,14 +2026,14 @@
 D.现代教育技术建设；</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>00097_单选题
 主张高等教育应以个人发展需要为出发点而制定教育目的、建构教育活动，这属于（     ）的高等教育目的观。
@@ -2060,14 +2043,14 @@
 D.人文主义；</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>00098_单选题
 高等教育的（     ）价值观主要观点是：高等教育的价值首先在于促进国家和社会的发展；高等教育的首要目标是培养公民、造就人才。
@@ -2077,14 +2060,14 @@
 D.英才教育；</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>00099_单选题
 高校中师生关系一般不能表现为（     ）关系。
@@ -2094,14 +2077,14 @@
 D.特殊；</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>00100_单选题
 高等学校教学评价主要作用有（     ）。
@@ -2111,14 +2094,14 @@
 D.评价作用、激励和改进作用。；</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>00101_单选题
 真正的大学（university）起源于（     ）。
@@ -2128,14 +2111,14 @@
 D.古希腊；</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>00102_单选题
 书院成为高等教育机构，始于（     ）。
@@ -2145,14 +2128,14 @@
 D.明代；</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>00103_单选题
 个别教学制的不足之处是（     ）。
@@ -2162,14 +2145,14 @@
 D.学生的积极性不够；</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>00104_单选题
 六六法是一种常见的（     ），适用于争议较大、学生感兴趣的问题，且简便有效。
@@ -2179,14 +2162,14 @@
 D.调查法；</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>00105_单选题
 （     ）取向的高等教育目的观主张培养为政治和经济服务的人才。
@@ -2196,14 +2179,14 @@
 D.大众教育；</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>00106_单选题
 首先提出“发现教学法”的学者是（     ）。
@@ -2213,14 +2196,14 @@
 D.布鲁姆（美）；</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>00107_单选题
 高等教育活动的第一要素和前提是（     ）。
@@ -2230,14 +2213,14 @@
 D.高等教育计划；</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>00108_单选题
 以科学精神为基础，以人文精神为价值取向的高等教育目的观是（     ）的高等教育目的观。
@@ -2247,14 +2230,14 @@
 D.实用主义；</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>00109_单选题
 教师主动请求用人单位解除聘任合同的行为是（     ）。
@@ -2264,31 +2247,14 @@
 D.辞聘；</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>00110_单选题
-（     ）是高等学校整个教学过程的最后一个环节，对教学起着检查、巩固和提高的作用。（该题目已移除！）
-A.实践教学；
-B.课程设计；
-C.毕业设计(论文)；
-D.毕业实习；</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>00111_单选题
 早期中世纪大学实行的是专业教育，主要围绕（     ）四科来组织教学活动。
@@ -2298,14 +2264,14 @@
 D.文法医神；</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>00112_单选题
 大学教师工作的特点主要表现在（     ）等几方面 。
@@ -2315,14 +2281,14 @@
 D.复杂性、创造性、长效性、独立性和协作性；</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>00113_单选题
 教育阻碍社会进步和个体发展的消极影响和作用是高等教育的（     ）。
@@ -2332,14 +2298,14 @@
 D.隐形功能；</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>00114_单选题
 按照著名学者马丁·特罗的划分标准，适龄人口高等教育入学率在（     ）为精英教育阶段。
@@ -2349,14 +2315,14 @@
 D.10%以下；</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>00115_单选题
 教育的终身化是（     ）教育的特征。
@@ -2366,14 +2332,14 @@
 D.20世纪；</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>00116_单选题
 个人本位的高等教育价值观的实质是主张高等教育的主要价值在于（     ）。
@@ -2383,14 +2349,14 @@
 D.为社会培养全人；</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>00117_单选题
 最早提出把服务社会作为大学重要职能的是（     ）。
@@ -2400,14 +2366,14 @@
 D.美国著名教育家哈佛大学校长科南特；</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>00118_单选题
 （     ）是高校的中心工作，是实现一定教育目的和人才培养目标的基本途径。
@@ -2417,14 +2383,14 @@
 D.人才培养；</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>00119_单选题
 让学生根据自己的具体情况而自定学习进度的教学方法称为（     ）。
@@ -2434,14 +2400,14 @@
 D.个性化教学法；</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>00120_单选题
 美国学者马丁特罗提出，当一国高等教育入学人数与适龄入学人口比率高于（     ）时，属于普及高等教育阶段。
@@ -2451,14 +2417,14 @@
 D.0.5；</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>00121_单选题
 校风、校训属于校园文化中的（     ）层面。
@@ -2468,14 +2434,14 @@
 D.行为文化；</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>00122_单选题
 高等教育与人类文化的关系是（     ）。
@@ -2485,14 +2451,14 @@
 D.互相包容的内在联系；</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>00123_单选题
 牛津、剑桥等英国古典大学具有悠久的（     ）传统。
@@ -2502,14 +2468,14 @@
 D.技能教育；</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>00124_单选题
 布鲁贝克认为，（     ）和政治论是高等教育存在的两大哲学基础。
@@ -2519,14 +2485,14 @@
 D.创造论；</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>00125_单选题
 从教育目的上来说，终身教育相较于传统教育，更注重（     ）。
@@ -2536,14 +2502,14 @@
 D.谋求各类教育间的联系与统一；</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>00126_单选题
 对教学活动现实的或潜在的价值作出判断的过程叫做（     ）。
@@ -2553,14 +2519,14 @@
 D.教学评价；</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>00127_单选题
 我国高等教育实行的管理体制是（     ）。
@@ -2570,14 +2536,14 @@
 D.部委管理制；</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>00128_单选题
 最早实行教学和科研相统一的大学是（     ）。
@@ -2587,14 +2553,14 @@
 D.剑桥大学；</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>00129_单选题
 大学生的兴趣具有（     ）的特征。
@@ -2604,14 +2570,14 @@
 D.成熟性与矛盾性；</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>00130_单选题
 （     ）是考试试题区分出学生能力水平差异程度的指标。
@@ -2621,14 +2587,14 @@
 D.区分度；</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>00131_单选题
 （     ）率先领导了19世纪世界高等教育发展史上大学职能的大变革。
@@ -2638,14 +2604,14 @@
 D.英国；</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>00132_单选题
 要善于鼓励学生独立完成毕业设计或论文，这体现了高校教师在指导学生进行毕业设计或论文时的（     ）。
@@ -2655,14 +2621,14 @@
 D.因材施教原则；</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>00133_单选题
 （     ）是学校人才培养目标与培养规格的具体化。
@@ -2672,14 +2638,14 @@
 D.学制设置；</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>00134_单选题
 法国的高等教育的管理体制结构属于（     ）。
@@ -2689,14 +2655,14 @@
 D.以上都不是；</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>00135_单选题
 高等教育应该培养既有（     ）又有文化素质，既有个人涵养又有公民素养、既有职业品质又有道德品质的新型创造性人才。
@@ -2706,31 +2672,14 @@
 D.综合素质；</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>00136_单选题
-（     ）的颁布，推动了美国赠地学院运动的兴起，引导了美国大学适应社会需求、服务社会的发展趋向。
-A.莫里尔法案；
-B.退伍军人法案；
-C.国防教育法案；
-D.高等教育方向法；</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>00137_单选题
 大学为社会服务的基本途径有传播知识、推广技术、提供信息和（     ）。
@@ -2740,14 +2689,14 @@
 D.专家服务；</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>00138_单选题
 （     ）的关系体现了高等教育过程中人与人关系中最基本、最重要的方面
@@ -2757,14 +2706,14 @@
 D.教师与家长；</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>00139_单选题
 培养人是高等教育的（     ），是我国高等教育目的的核心要旨。
@@ -2774,14 +2723,14 @@
 D.最高目标；</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>00140_单选题
 “坚持育人为本、德育为先，实施素质教育，提高教育现代化水平，培养德智体美全面发展的社会主义建设者和接班人，办好人民满意的教育”是（     ）提出的。
@@ -2791,14 +2740,14 @@
 D.党的十八大；</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>00141_单选题
 我国高等教育目的坚持的基本立场是（     ）。
@@ -2808,14 +2757,14 @@
 D.培养理性人；</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>00142_单选题
 晚清设立的（     ）是我国近代第一所国立大学。
@@ -2825,14 +2774,14 @@
 D.京师大学堂；</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>00143_单选题
 高校课程建设的重点应该是：（     ）。
@@ -2842,14 +2791,14 @@
 D.重视课程管理；</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>00144_单选题
 规定高等教育的主要任务是培养具有创新精神和实践能力的高级专门人才的是（     ）。
@@ -2859,14 +2808,14 @@
 D.1998年《中华人民共和国高等教育法》；</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>00145_单选题
 首先提出“教学与科研统一”的新型教育原则而发展了大学科研职能的是：（     ）。
@@ -2876,14 +2825,14 @@
 D.德国柏林大学；</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>00146_单选题
 将学生应掌握的知识、能力的总体分解成各“小单元”，并分别确定为必修与选修两大门类，规定每门课程的学分和取得该专业毕业应修满的总学分的教学管理制度称为（     ）。
@@ -2893,14 +2842,14 @@
 D.学制；</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>00147_单选题
 学分制的缺点之一是（     ）。
@@ -2910,14 +2859,14 @@
 D.难以发挥学生的特长；</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>00148_单选题
 1632年出版的高等教育研究著作《大教学论》的作者是（     ）。
@@ -2927,14 +2876,14 @@
 D.赫尔巴特；</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>00149_单选题
 教育与生产力发展的不平衡性说明教育具有（     ）。
@@ -2944,14 +2893,14 @@
 D.相对独立性；</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>00150_单选题
 高等教育国际化的重要特征是大学生（     ）。
@@ -2961,14 +2910,14 @@
 D.使用原版教材的数量；</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>00151_单选题
 从职能上讲，大学的根本使命是（     ）。
@@ -2978,14 +2927,14 @@
 D.发展科学；</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>00152_单选题
 美国开设的第一所高校是（     ）。
@@ -2995,14 +2944,14 @@
 D.威廉玛丽学院；</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>00153_单选题
 （     ）是教育活动中最基本和最核心的位置。
@@ -3012,14 +2961,14 @@
 D.课程；</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>00154_单选题
 高等学校整个教学过程中的最后一个基本环节是（     ）。
@@ -3029,14 +2978,14 @@
 D.毕业设计或毕业论文；</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>00155_单选题
 用人单位因某种原因不宜继续聘任教师，双方解除合同关系是（     ）。
@@ -3046,14 +2995,14 @@
 D.辞聘；</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>00156_单选题
 民国时期“大学区制”是蔡元培仿效（     ）高等教育系统设立的。
@@ -3063,48 +3012,14 @@
 D.英国；</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>00157_单选题
-美国高等学校教师聘任制度中，一般是在（     ）阶段进入“终身制轨道(Tenure)”。（该题目已移除！）
-A.教授；
-B.副教授；
-C.助理教授；
-D.博士后；</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>00158_单选题
-（     ）是教育活动中最基本和最核心的位置。（该题目已移除！）
-A.教师和学生；
-B.教育手段；
-C.教育方法；
-D.课程；</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>00159_单选题
 以学群、学类为组织进行综合知识教学的筑波模式，以跨学科选课为主要特征的麻省理工学院（MIT）模式，以及通过复合课程将文、理学科融为一体的牛津模式，三种模式（     ）。
@@ -3114,14 +3029,14 @@
 D.课程性质职业化趋势；</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>00160_单选题
 一般认为，现代高等学校的直接源头是（     ）。
@@ -3131,14 +3046,14 @@
 D.中国“太学”；</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>00161_单选题
 唐代官学教育的主干是（     ）。
@@ -3148,14 +3063,14 @@
 D.诗赋；</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>00162_单选题
 下列（     ）是中国殷商时期高层次的学问传授中心。
@@ -3165,14 +3080,14 @@
 D.书院；</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>00163_单选题
 高校要实现自身的基本职能，主要依靠的是（     ）。
@@ -3182,14 +3097,14 @@
 D.大学生家长；</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>00164_单选题
 从作用的呈现形式看，高等教育功能可分为（     ）。
@@ -3199,14 +3114,14 @@
 D.谋生功能和享用功能；</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>00165_单选题
 统一要求与因材施教相结合原则是由学生（     ）的规律所决定的。
@@ -3216,14 +3131,14 @@
 D.身心发展共性与个性对立统一；</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>00166_单选题
 高等教育活动越来越成为一种主动或潜在的社会服务活动亦即促进社会发展的功能，由此也产生了高等学校直接或间接（     ）的职能。
@@ -3233,14 +3148,14 @@
 D.提升人才品质；</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>00167_单选题
 高校课堂教学质量评价的指标体系不包括（     ）。
@@ -3250,31 +3165,14 @@
 D.领导或督导员的评价指标体系；</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>00168_单选题
-1632年出版的高等教育研究著作《大教学论》的作者是：（     ）。（该题目已移除！）
-A.夸美纽斯（捷克）；
-B.纽曼（英国）；
-C.皮洛戈夫（俄国）；
-D.保尔森(德国)；</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>00169_单选题
 价值取向是当代大学生的内心向导，它对当代大学生承担新世纪赋予的历史使命具有重要影响。当前，高校学生价值取向的变化特点是（     ）。
@@ -3284,14 +3182,14 @@
 D.兼容性、主体性、多样性、矛盾性、时代性、不稳定性；</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>00170_单选题
 高等教育对人所起的作用，也就是高等教育要促进人的（     ）发展。
@@ -3301,14 +3199,14 @@
 D.综合能力；</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>00171_单选题
 （     ）是衡量考试结果的稳定性和可靠性程度的指标。
@@ -3318,14 +3216,14 @@
 D.区分度；</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>00172_单选题
 （     ）是课堂教学的中心环节。
@@ -3335,14 +3233,14 @@
 D.课后总结；</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>00173_单选题
 大学的管理中心是（     ）。
@@ -3352,14 +3250,14 @@
 D.班级；</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>00174_单选题
 中国近代第一所具有高等教育性质与功能的学校是（     ）。
@@ -3369,14 +3267,14 @@
 D.京师大学堂；</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>00175_单选题
 学分制的主要缺点之一是（     ）。
@@ -3386,14 +3284,14 @@
 D.不利于教师发挥特长；</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>00176_单选题
 “教师中心论”的代表人物是：（     ）。
@@ -3403,14 +3301,14 @@
 D.凯洛夫；</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>00177_单选题
 教育的结构变化主要表现在（     ）等方面。
@@ -3420,14 +3318,14 @@
 D.综合型大学、教学型大学、研究型大学、教学研究理大学；</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>00178_单选题
 提出“大学向所有人开放，向所有学科开放”的办学思想的是：（     ）。
@@ -3437,14 +3335,14 @@
 D.美国哈佛大学；</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>00179_单选题
 人们溯源现代高等学校时，一般都认为是（     ）。
@@ -3454,14 +3352,14 @@
 D.资产阶级工业革命时期；</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>00180_单选题
 高校教师借助学科、专业范围内的行业自律、同行交流的教学发展模式，称为（     ）。
@@ -3471,14 +3369,14 @@
 D.专家介入模式；</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>00181_单选题
 高等教育的萌芽阶段，一般认为是在西方（     ）时代。
@@ -3488,14 +3386,14 @@
 D.文艺复兴；</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>00182_单选题
 以下不属于高等教育的政治正向功能的是（     ）。
@@ -3505,14 +3403,14 @@
 D.抵制政治变革，维护政治稳定；</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>00183_单选题
 高校内部权力重心明显倾向于基层教学和研究单位，并深刻体现了学术权威影响的高校管理模式是（     ）。
@@ -3522,14 +3420,14 @@
 D.日本模式；</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>00184_单选题
 通识教育一般理解为（     ）。
@@ -3539,14 +3437,14 @@
 D.通识教育不仅强调宽口径，而且重视不同学科知识的融会贯通；</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>00185_单选题
 （     ）是高校整个教学过程中的最后一个基本环节，是整个教学过程的总结。
@@ -3556,14 +3454,14 @@
 D.毕业设计(论文)；</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>00186_单选题
 按照马克思主义的观点，促成人的全面发展的惟一方法是（     ）。
@@ -3573,14 +3471,14 @@
 D.注重实践教学；</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>00187_单选题
 1978年，我国的第一个专门的高等教育研究机构是（     ）的高等教育科学研究室。
@@ -3590,14 +3488,14 @@
 D.山东大学；</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>00188_单选题
 确定教育目的的客观依据是（     ）。
@@ -3607,14 +3505,14 @@
 D.生产力和科技发展水平；</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>00189_单选题
 提出“多元化巨型大学”概念的当代著名高等教育思想家是（     ）。
@@ -3624,14 +3522,14 @@
 D.弗莱克斯纳；</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>00190_单选题
 赫钦斯认为：“不论学生是否注定从事于沉思的生活或实际的生活，由理智美德的培养所组成的教育是最有用的教育”，这体现的是（     ）的高等教育目的观。
@@ -3641,14 +3539,14 @@
 D.实用主义；</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>00191_单选题
 一般认为，现代大学源于中世纪大学，最早的中世纪大学有波伦亚大学、萨莱诺大学和（     ）。
@@ -3658,14 +3556,14 @@
 D.那不勒斯大学；</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>00192_单选题
 现代高等学校的三大职能是：（     ）。
@@ -3675,14 +3573,14 @@
 D.第一，教学；第二、科研；第三，为社会服务；</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>00193_单选题
 到2009年，我国高等教育在校人数总规模达2979万人，高等教育的毛入学率达到百分之二十四点二，已跨入国际公认的高等教育（     ）阶段。
@@ -3692,14 +3590,14 @@
 D.精英教育阶段；</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>00194_单选题
 目前我国高等学校课堂教学最普遍采用的方法是（     ）。
@@ -3709,14 +3607,14 @@
 D.计算机教学法；</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>00195_单选题
 主张以经济发展需要为出发点而制定高等教育目的、构建教高等育活动，这属于（     ）的高等教育目的观。
@@ -3726,14 +3624,14 @@
 D.人文主义；</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>00196_单选题
 马丁·特罗把高等教育发展分成三个阶段，当一个国家高等教育所接纳的学生数与适龄青年的比率在50%以上时，为（     ）阶段。
@@ -3743,14 +3641,14 @@
 D.全球高等教育；</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>00197_单选题
 （     ）的创立，使德国大学的理念发生了划时代地转折。
@@ -3760,14 +3658,14 @@
 D.柏林大学；</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>00198_单选题
 运用榜样教育法应把握三点：所选择的榜样具有先进性，善于发挥榜样的模范作用，发挥（     ）的榜样作用。
@@ -3777,14 +3675,14 @@
 D.家长；</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>00199_单选题
 人文主义特别推崇理性，将理性视为人兽之别的根本判据。人文主义所强调的理性不是工具理性和科学理性，而是（     ），即人性和道德意义上的理性。
@@ -3794,14 +3692,14 @@
 D.社会理性；</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>00200_单选题
 科学主义教育目的观最显著的特质是重视（     ）。
@@ -3811,14 +3709,14 @@
 D.学校的科学技术教育；</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>00201_单选题
 （     ）是高等教育所具有的功效以及能够发挥这种功效的能力的总称。
@@ -3828,14 +3726,14 @@
 D.高等学校职能；</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>00202_单选题
 以一定的理论和事实为依据，对所研究的课题提出某种带有推测和假定意义上的理论解释和结论是（     ）。
@@ -3845,14 +3743,14 @@
 D.课题想象；</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>00203_单选题
 “通过研究进行教学”是（     ）。
@@ -3862,14 +3760,14 @@
 D.我国古代书院确立的原则；</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>00204_单选题
 在高校外部，教育行政部门的行政化管理的特点不包括（     ）。
@@ -3879,14 +3777,14 @@
 D.我国教育行政部门的行政化管理广泛存在于高校办学的各个环节；</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>00205_单选题
 确定高校德育目标的关键依据是（     ）。
@@ -3896,14 +3794,14 @@
 D.邓小平思想和理论；</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>00206_单选题
 根据各级各类学校任务确定的对所培养对象的特殊要求叫做（     ）。
@@ -3913,14 +3811,14 @@
 D.培养目的；</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>00207_单选题
 自然科学与社会科学受到空前重视，导致了哲学博士学位在（     ）新型大学中应运而生。
@@ -3930,14 +3828,14 @@
 D.英国；</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>00208_单选题
 当前我国高校毕业生就业制度是（     ）。
@@ -3947,14 +3845,14 @@
 D.自主择业；</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>00209_单选题
 人的社会化的重要内容是（     ），它使个体树立社会所向往的政治理想，形成维护现行政治制度的政治行为。
@@ -3964,14 +3862,14 @@
 D.多样化；</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>00210_单选题
 （     ）是系统论述教育的经济功能的经济学者。他在其名著《国民财富的性质和原因的研究》一书中，系统论述了其教育经济思想。
@@ -3981,14 +3879,14 @@
 D.亚当斯密；</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>00211_单选题
 持个人本位论的高等教育目的观的教育家是（     ）。
@@ -3998,14 +3896,14 @@
 D.纳托尔普；</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>00212_单选题
 2001年，江泽民在建党80周年庆祝大会上的讲话中提出了“培育一代又一代有理想、有道德、有文化、有纪律的公民”的观点，此后（     ）进入了高等教育目标序列中。
@@ -4015,14 +3913,14 @@
 D.培育四有人才；</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>00213_单选题
 高等学校的职能是高等教育功能的（     ），是把高等学校作为一种机构并针对外部环境而言的。
@@ -4032,14 +3930,14 @@
 D.特殊化；</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>00214_单选题
 高等教育过程中的研究活动，即（     ）的功能衍生出高等学校发展科学的职能。
@@ -4049,14 +3947,14 @@
 D.保存文化；</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>00215_单选题
 评价教师在课堂教学中表现出来的真诚、热情、民主的程度，属于教学评价中的（     ）方面评价。
@@ -4066,14 +3964,14 @@
 D.情感；</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>00216_单选题
 我国高等学校的教学计划一般是按（     ）制定的。
@@ -4083,14 +3981,14 @@
 D.专业；</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>00217_单选题
 依据办学主体的不同，下列国家中，高等教育办学形式结构属于私立主导型的是（     ）。
@@ -4100,14 +3998,14 @@
 D.日本；</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>00218_单选题
 从狭义来说，（     ）是指各级各类学校为了实现培养目标而开设的学科及其目的、内容、范围、活动、进程等的总和。
@@ -4117,14 +4015,14 @@
 D.课程；</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>00219_单选题
 （     ）是对学生达到教学目标要求的程度、即对知识和能力掌握程度的评定。
@@ -4134,14 +4032,14 @@
 D.学业成绩考核；</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>00220_单选题
 中世纪欧洲大学中影响巨大的样板学校是（     ）。
@@ -4151,14 +4049,14 @@
 D.达勒姆大学；</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>00221_单选题
 提出“威斯康星思想”的著名高等教育思想家是（     ）。
@@ -4168,14 +4066,14 @@
 D.范·海斯；</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>00222_单选题
 把科学原理变成改造世界的能动力量的研究是（     ）。
@@ -4185,14 +4083,14 @@
 D.人文科学研究；</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>00223_单选题
 美国哈佛大学将培养（     ）作为大学“合理的标准”。
@@ -4202,31 +4100,14 @@
 D.有追求的人；</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>00224_单选题
-（     ）是高校整个教学过程中的最后一个基本环节，是整个教学过程的总结。（该题目已移除！）
-A.课堂教学；
-B.实验操作；
-C.毕业实习；
-D.毕业设计(论文)；</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>00225_单选题
 根据比格斯的研究，学习动机可分为三种类型：工具性动机、内在动机和成就动机，这三种动机分别对应于哪三种学习策略？（     ）
@@ -4236,14 +4117,14 @@
 D.意义策略、组织策略和目标策略；</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>00226_单选题
 （     ）是高等学校的中心任务。
@@ -4253,14 +4134,14 @@
 D.文化传承；</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>00227_单选题
 （     ）是高等教育的根本立足点，也是高等教育价值的根本所在。
@@ -4270,14 +4151,14 @@
 D.培养人；</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>00228_单选题
 在中国，高等教育从萌芽走向雏型的标志是：（     ）。
@@ -4287,14 +4168,14 @@
 D.唐宋时期的“书院教育”；</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>00229_单选题
 从教育发展的历史进程来看，高等教育普及化的进程始于（     ）。
@@ -4304,14 +4185,14 @@
 D.知识经济时代；</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>00230_单选题
 高等教育通过培养各种专业人才，通过高等学校提供的科学技术成果和直接为经济服务的各种活动来实现自己的（     ）。
@@ -4321,14 +4202,14 @@
 D.推动社会发展功能；</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>00231_单选题
 教师根据教学需要，从教材入手，提出一定的问题，引导学生对问题进行思考和分析，通过寻求问题的解决来激发学生学习的积极性，从而掌握知识的教学方法属于（     ）。
@@ -4338,14 +4219,14 @@
 D.程序教学法；</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>00232_单选题
 高等教育活动的始点、中点、和终点是（     ）。
@@ -4355,14 +4236,14 @@
 D.高等教育效果；</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>00233_单选题
 （     ）研究具有明确性、可行性、风险性和商业性等特点。
@@ -4372,14 +4253,14 @@
 D.开发；</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>00234_单选题
 高校课程评估的内容不包括（     ）。
@@ -4389,14 +4270,14 @@
 D.教学实施过程；</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>00235_单选题
 西方近现代高等教育始于：（     ）。
@@ -4406,14 +4287,14 @@
 D.“雅典大学”；</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>00236_多选题
 教学反思的具体方法有如下几种（     ）。
@@ -4424,14 +4305,14 @@
 E.接触新知；</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>00237_多选题
 关于各国高校课程改革的共同性背景和动因，正确的说法是（     ）。
@@ -4442,14 +4323,14 @@
 E.互联网在教学中的应用；</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>00238_多选题
 我国的学位制度包括（     ）等几级学位。
@@ -4459,14 +4340,14 @@
 D.博士后；</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>00239_多选题
 与高等教育终身化相关的概念包括（     ）。
@@ -4476,14 +4357,14 @@
 D.学会生活；</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>00240_多选题
 教师专业的基本特点是（     ）。
@@ -4494,14 +4375,14 @@
 E.发展渐进性；</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>00241_多选题
 高校教师评价可分为（     ）。
@@ -4511,14 +4392,14 @@
 D.教学绩效评价；</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>00242_多选题
 高等教育的结构变化主要体现在（     ）等方面。
@@ -4528,14 +4409,14 @@
 D.课程结构；</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>00243_多选题
 以学科或专业为基础，分门别类地培养高级专门人才的教育是（     ）。
@@ -4545,14 +4426,14 @@
 D.基础教育；</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>00244_多选题
 高等教育的人口功能表现为（     ）。
@@ -4562,14 +4443,14 @@
 D.加速人口的城镇化；</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>00245_多选题
 目前，我国高等学校的教学计划一般是按专业制定的。一个完整的教学计划主要应包括（     ）内容。
@@ -4580,14 +4461,14 @@
 E.学时安排；</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>ACDE</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>00246_多选题
 按照办学主体的不同，高等教育办学形式结构可以概括为（     ）三种类型。
@@ -4597,14 +4478,14 @@
 D.自由市场型；</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>00247_多选题
 高校教师的任务主要有以下几个方面：（     ）。
@@ -4614,14 +4495,14 @@
 D.为社会服务；</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>00248_多选题
 对于高校培养目标的表述，下列选项中正确的是（     ）。
@@ -4631,14 +4512,14 @@
 D.培养目标决定着教育实践活动的性质、形式内容和方向；</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>00249_多选题
 大学教师工作的特点是（     ）。
@@ -4648,14 +4529,14 @@
 D.高度复杂性；</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>00250_多选题
 汉代以后，中国官办的高等教育机构被称为（     ）。
@@ -4665,14 +4546,14 @@
 D.书院；</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>00251_多选题
 我国高等教育管理体制改革的重点和基本方向有（     ）。
@@ -4682,14 +4563,14 @@
 D.扩大高校办学的自主权，增强学校的活力。；</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>00252_多选题
 学制是指一个国家的各级各类学校的系统，它包括（     ）等等。高等学校的学制即指各类各层次高等学校的系统，是学校教育制度的一个组成部分。
@@ -4700,14 +4581,14 @@
 E.各级各类学校之间的关系；</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>ABCDE</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>00253_多选题
 中世纪大学具有的重要特征包括（     ）。
@@ -4717,14 +4598,14 @@
 D.专业性和学术性；</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>00254_多选题
 从狭义上说课程主要体现在（     ）。
@@ -4734,14 +4615,14 @@
 D.教案；</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>00255_多选题
 素质教育的全面发展观包括（     ）。
@@ -4751,14 +4632,14 @@
 D.教师和学生一起成长；</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>00256_多选题
 建立新型的师生关系，对教师来说，可以采用哪些策略？（     ）
@@ -4768,14 +4649,14 @@
 D.提高自我修养，健全自身人格；</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>00257_多选题
 高等教育经历了萌芽、（     ）几个阶段。
@@ -4785,14 +4666,14 @@
 D.扩展；</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>00258_多选题
 国际21世纪教育委员会向联合国教科文组织提交的报告提出21世纪教育的四大支柱是（     ）。
@@ -4802,14 +4683,14 @@
 D.学会生存；</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>00259_多选题
 教学评价的类型有（     ）。
@@ -4819,14 +4700,14 @@
 D.终结性评价；</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>00260_多选题
 一般来说，课程建设的评价指标包括（     ）师资条件、教学效果等。
@@ -4837,14 +4718,14 @@
 E.教学职责；</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>ABE</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>00261_多选题
 近年来，我国高等教育在大众化进程中的标志是（     ）。
@@ -4855,14 +4736,14 @@
 E.教学内容多样化；</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>ABCE</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>00262_多选题
 讲授法是教师通过口头语言表述、讲解、讲演等形式，系统地向学生传授知识的方法，其优点主要有（     ）。
@@ -4873,14 +4754,14 @@
 E.学生通过接触实际，独立观察，能获得丰富的感性材料；</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>00263_多选题
 高等学校社会服务的类型和方式主要有（     ）。
@@ -4891,14 +4772,14 @@
 E.建立教育-科研-生产联合体和高新技术产业；</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>00264_多选题
 科学主义课程思潮对大学课程带来的变化有（     ）。
@@ -4909,14 +4790,14 @@
 E.促使大学课程注重经典；</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>00265_多选题
 下列国家中，高等教育宏观管理体制属于中央集权型的是（     ）。
@@ -4926,14 +4807,14 @@
 D.日本；</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>00266_多选题
 高校教育要帮助大学生树立现代的、正确的人生发展观，需要做到以下观念的转变（     ）。
@@ -4943,14 +4824,14 @@
 D.择业观的转变；</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>00267_多选题
 柏林大学主要的办学特色是（     ）。
@@ -4960,14 +4841,14 @@
 D.教研结合；</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>BD</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>00268_多选题
 高校教师学习高等教育学的意义有（     ）。
@@ -4977,14 +4858,14 @@
 D.形成专业发展观；</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>00269_多选题
 讲授法的优点有（     ）。
@@ -4994,14 +4875,14 @@
 D.能寓思想教育于讲授之中，具有较强的感染力；</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>00270_多选题
 下列属于雅典教育中“七艺”的是（     ）。
@@ -5011,14 +4892,14 @@
 D.几何学；</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>00271_多选题
 课程内容的选择应遵循如下原则（     ）。
@@ -5029,14 +4910,14 @@
 E.量力和满足原则；</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>00272_多选题
 关于教育本质的论述有（     ）。
@@ -5046,14 +4927,14 @@
 D.是一种有意识、有目的的专门培养人的社会实践活动；</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>00273_多选题
 高等教育评价的功能包括（     ）。
@@ -5063,14 +4944,14 @@
 D.反馈——调节功能；</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>00274_多选题
 我国高等教育体制改革的目标是要改变以下弊端（     ）。
@@ -5080,31 +4961,14 @@
 D.条块分割；</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>00275_多选题
-课程的功能有（     ）。（该题目已移除！）
-A.评价功能；
-B.激励功能；
-C.育人功能；
-D.文化功能；</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>CD</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>00276_多选题
 高校隐性课程的建设应着重抓好哪几个方面的工作？（     ）
@@ -5115,14 +4979,14 @@
 E.增设职业性课程或专业；</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>00277_多选题
 高等学校校园文化通常分为以下几个层面，即（     ）。
@@ -5132,14 +4996,14 @@
 D.行为文化；</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>00278_多选题
 我国高校课程表现出的基本形式有（     ）。
@@ -5150,14 +5014,14 @@
 E.课程目标；</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>00279_多选题
 高校教师评估的渠道主要包括（     ）。
@@ -5167,14 +5031,14 @@
 D.领导和督导员的评估；</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>00280_多选题
 高等教育目的作用主要表现在（     ）等几个方面。
@@ -5185,14 +5049,14 @@
 E.具有评价作用；</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>BCDE</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>00281_多选题
 美国的博士学位包括（     ）等几种类型。
@@ -5202,14 +5066,14 @@
 D.理科博士学位；</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>00282_多选题
 高等教育管理体制则是国家管理高等教育的（     ）的总称。
@@ -5220,14 +5084,14 @@
 E.制度；</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>BDE</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>00283_多选题
 广义的课程评价涉及到下列哪几个方面？（     ）
@@ -5238,14 +5102,14 @@
 E.对课程设置的评价；</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>00284_多选题
 关于教学与科研之间的关系，下列说法正确的是（     ）。
@@ -5255,14 +5119,14 @@
 D.教学与科研很难两全其美；</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>00285_多选题
 以下关于高等教育的表述，正确的是（     ）。
@@ -5272,14 +5136,14 @@
 D.培养高级专门人才的教育；</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>00286_多选题
 讲授法是教师通过（     ）等形式，系统地向学生传授知识的方法，是目前我国高等学校教学最普遍采用的方法。
@@ -5290,14 +5154,14 @@
 E.讨论；</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>00287_多选题
 下列选项属于高等教育评价的基本原则的是（     ）。
@@ -5307,14 +5171,14 @@
 D.激励性原则；</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>00288_多选题
 按照著名学者马丁·特罗的划分标准，高等教育发展包括以下（     ）等三个阶段。
@@ -5324,14 +5188,14 @@
 D.终身化；</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>00289_多选题
 高等学校的科研性服务的主要形式有（     ）。
@@ -5342,14 +5206,14 @@
 E.参与科技市场建设，实现科技成果转化；</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>CDE</t>
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>00290_多选题
 教学过程是教师引导下学生的特殊认识过程，表现出在（     ）。
@@ -5359,14 +5223,14 @@
 D.重复性；</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>00291_多选题
 下列（     ）学科属于人文科学研究领域的范畴。
@@ -5376,14 +5240,14 @@
 D.法律学；</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>00292_多选题
 我国高等教育评估的变革策略包括（     ）。
@@ -5393,14 +5257,14 @@
 D.改革评估方法，调动被评对象参与评估的积极性；</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>00293_多选题
 近年来，我国高等教育一直在（     ）。
@@ -5410,14 +5274,14 @@
 D.加强行政化；</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>00294_多选题
 高校师生关系主要表现为以下几种形式（     ）。
@@ -5427,14 +5291,14 @@
 D.法律关系；</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>00295_多选题
 案例教学的优点是（     ）。
@@ -5444,14 +5308,14 @@
 D.培养学生分析和解决实际问题的能力；</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>00296_多选题
 教学计划目标的确立以专业培养目标为基础专业培养目标的具体内容包括（     ）。
@@ -5462,14 +5326,14 @@
 E.重点难点；</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>00297_多选题
 按照高校的三大职能，教师职业角色主要是（     ）。
@@ -5480,14 +5344,14 @@
 E.创业者角色；</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>00298_多选题
 课程的功能有（     ）。
@@ -5498,14 +5362,14 @@
 E.政治功能；</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>00299_多选题
 “一日为师，终身为父”反映了师生关系中的（     ）。
@@ -5515,14 +5379,14 @@
 D.师道尊严；</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>00300_多选题
 我国高等教育评估中存在的问题主要有（     ）。
@@ -5532,14 +5396,14 @@
 D.重视总结性评估，忽视过程性评估；</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>00301_多选题
 高等教育评价的意义主要有（     ）。
@@ -5549,14 +5413,14 @@
 D.加强对高等学校教育的宏观指导与管理；</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>00302_多选题
 下列国家中，高等教育宏观管理体制属于集权与分权结合型的是（     ）。
@@ -5566,14 +5430,14 @@
 D.英国；</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>00303_多选题
 高等教育的发展趋势主要表现在（     ）。
@@ -5583,14 +5447,14 @@
 D.管理法制化和教学手段现代化；</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>00304_多选题
 《高等教育法》对高校领导体制内涵的规定，包括（     ）。
@@ -5600,14 +5464,14 @@
 D.民主管理和监督；</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>00305_多选题
 高等学校的学制结构一般是指高等学校的（     ）。
@@ -5618,14 +5482,14 @@
 E.层次结构；</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
+    <row r="298">
+      <c r="A298" t="inlineStr">
         <is>
           <t>00306_多选题
 欧洲中世纪大学的主要学科分科包括（     ）等几大学科。
@@ -5635,14 +5499,14 @@
 D.医学；</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>00307_多选题
 课程主要体现在（     ）之中。
@@ -5653,14 +5517,14 @@
 E.教科书；</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>CDE</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
+    <row r="300">
+      <c r="A300" t="inlineStr">
         <is>
           <t>00308_多选题
 实现高等教育目的的途径（     ）。
@@ -5670,14 +5534,14 @@
 D.美育是实现高等教育目的的动力支持；</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>00309_多选题
 专业属性或标准可概括为（     ）。
@@ -5688,14 +5552,14 @@
 E.他律性与发展性；</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>00310_多选题
 下列关于教学方法的叙述，正确的有（     ）。
@@ -5705,14 +5569,14 @@
 D.方法的选用须注意到学生的特点；</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>00311_多选题
 按教学评价的不同目的、作用和时间来分，教学评价主要有（     ）三种类型。
@@ -5722,14 +5586,14 @@
 D.诊断性评价；</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>00312_多选题
 美国大学教师的学衔等级包括（     ）等几级。
@@ -5739,14 +5603,14 @@
 D.博士后；</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>00313_多选题
 下列国家中，按照办学主体的不同，高等教育办学形式结构属于双轨型的包括（     ）。
@@ -5756,14 +5620,14 @@
 D.荷兰；</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>00314_多选题
 教学中教师的主导和学生的主动性性相结合的教学原则要求教师做到：（     ）。
@@ -5773,14 +5637,14 @@
 D.对学生科学方法的指导；</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>00315_多选题
 在贯彻传授知识与培养能力相结合原则时，要求做到（     ）。
@@ -5791,14 +5655,14 @@
 E.在尊重学生的基础上对学生提出严格的要求；</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>00316_多选题
 从历史上看，许多政治事件常常从学校发端，如（     ）。
@@ -5808,14 +5672,14 @@
 D.“四人帮”覆灭；</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>00317_多选题
 高等教育国际化的特征是（     ）。
@@ -5825,14 +5689,14 @@
 D.办学主体的国际化；</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>00318_多选题
 高等教育除了传统上的培养人才、发展科学、服务社会三大职能以外，目前学术界补充提出了一些新的功能，如（     ）。
@@ -5842,14 +5706,14 @@
 D.保护环境；</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>00319_多选题
 高校教师的主要任务有：（     ）。
@@ -5859,14 +5723,14 @@
 D.积极创收；</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>00320_多选题
 经济发展对高等教育的制约作用有哪些？（     ）
@@ -5877,14 +5741,14 @@
 E.经济发展水平制约着高等教育的内容和手段；</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>ABE</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>00321_多选题
 课程的文化功能包括（     ）。
@@ -5894,14 +5758,14 @@
 D.创造文化的功能；</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>00322_多选题
 高等教育评价的内容包括（     ）。
@@ -5911,14 +5775,14 @@
 D.高等学校的学生评估；</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>00323_多选题
 高等学校社会服务的原则有（     ）。
@@ -5929,14 +5793,14 @@
 E.放宽搞活和严格管理相结合；</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>00324_多选题
 1810年柏林大学首先提出了“通过研究进行教学”、（     ）的新型教育原则。
@@ -5947,14 +5811,14 @@
 E.“独立与自由统一”；</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>00325_多选题
 在普通高等学校本科教学工作水平评估的过程中，自始至终贯彻的原则是（     ），以较好地发挥评估的导向作用和诊断作用。
@@ -5964,14 +5828,14 @@
 D.重在建设；</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>00326_多选题
 课程体系改革应处理好的几个关系是（     ）。
@@ -5982,14 +5846,14 @@
 E.专业定向与分流培养的关系。；</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>ABCDE</t>
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>00327_多选题
 高等教育对经济的贡献主要表现在（     ）。
@@ -5999,14 +5863,14 @@
 D.经济发展速度影响高等教育发展；</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>00328_多选题
 当前我国高等教育要树立（     ）的高等教育质量观。
@@ -6016,14 +5880,14 @@
 D.特色化；</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>00329_多选题
 制定高校培养目标的依据有哪些？（     ）
@@ -6033,14 +5897,14 @@
 D.社会需求与人的发展需求的统一；</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>00330_多选题
 高校规章制度对学校发展的作用主要体现在（     ）。
@@ -6051,14 +5915,14 @@
 E.有助于发扬学校民主；</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>00331_多选题
 高校课堂教学质量评估的基本内容主要有（     ）。
@@ -6068,14 +5932,14 @@
 D.教学效果是否良好；</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>00332_多选题
 高等学校具有（     ）基本职能。
@@ -6086,14 +5950,14 @@
 E.传播思想；</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>00333_多选题
 下列（     ）学科属于社会科学研究领域的范畴。
@@ -6103,14 +5967,14 @@
 D.法律学；</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>00334_多选题
 确立大学生的主体地位，我们应该（     ）。
@@ -6120,14 +5984,14 @@
 D.塑造大学生的主体人格；</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>00335_多选题
 教育的政治功能有（     ）。
@@ -6137,14 +6001,14 @@
 D.高等教育通过培养具有一定政治态度、思想意识的人，在维护和巩固一定的政治制度中发挥积极作用；</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>00336_多选题
 高校师生关系体现了高等教育过程中人与人关系中最基本、最重要的方面。两者关系主要表现为（     ）。
@@ -6155,14 +6019,14 @@
 E.道德伦理关系；</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>ADE</t>
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>00337_多选题
 大学生主体地位的表现有（     ）。
@@ -6172,14 +6036,14 @@
 D.独立的个体；</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>00338_多选题
 关于讲授法的缺点，叙述正确的有（     ）。
@@ -6189,14 +6053,14 @@
 D.记忆效果差，尤其是时间较长的讲授课；</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>00339_多选题
 评价一堂课中教师的教学行为主要涉及（     ）等三个方面。
@@ -6206,14 +6070,14 @@
 D.技能与习惯；</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>00340_多选题
 高等教育学的研究对象为（     ）。
@@ -6223,14 +6087,14 @@
 D.高等教育规律；</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>00341_多选题
 高等教育对人口的影响是深远的、多方面的，后果是积极的、有益的，其具体功能表现在如下哪些方面？（     ）
@@ -6241,14 +6105,14 @@
 E.高等教育是控制人口增长的手段之一。；</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>BDE</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>00342_多选题
 对头脑风暴法叙述正确的是：（     ）。
@@ -6258,14 +6122,14 @@
 D.可使学生在较短时间内表现出高水准；</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>00343_多选题
 高校科研按活动对象分，包括（     ）。
@@ -6276,30 +6140,134 @@
 E.人文科学研究；</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ABE</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>00344_判断题
+效度指的是考试结果的稳定性和可靠性程度。</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>00345_判断题
+高等教育是一种充满各种矛盾的实践活动，最根本的就是高等教育与人的发展、社会的发展之间的矛盾。</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>00346_判断题
+“211、985工程”是以建设世界一流大学及世界高水平大学为目的而设立的。</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>00347_判断题
+我国高等教育评估主体与评估对象之间的关系多是单向性关系，评估主体主要以被评估对象所呈现的材料为主要信息源。</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>00348_判断题
+1810年，柏林大学首先提出“通过过研究进行教学”“教学与科研统一”和“独立于自由统一”的新型教育原则。</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>00349_判断题
+欧洲中世纪大学起源于学者行会，包括教师行会和学生行会。</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>00350_判断题
+英国高等教育具有悠久的专业教育传统。</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>00351_判断题
+我国目前的高等教育宏观管理体制是“两级管理、分级负责、以省级为主”的体制。</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ABE</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>00344_判断题
-效度指的是考试结果的稳定性和可靠性程度。</t>
+          <t>00352_判断题
+梅贻琦任清华校长期间，极为重视教学与研究的统一。</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>00345_判断题
-高等教育是一种充满各种矛盾的实践活动，最根本的就是高等教育与人的发展、社会的发展之间的矛盾。</t>
+          <t>00353_判断题
+高等学校课程管理主要包括课程制定者的管理、课程编制内容的管理以及课程编制活动的管理。</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6311,8 +6279,8 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>00346_判断题
-“211、985工程”是以建设世界一流大学及世界高水平大学为目的而设立的。</t>
+          <t>00354_判断题
+科学研究是高校发展的基础和支撑点。</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6324,34 +6292,34 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>00347_判断题
-我国高等教育评估主体与评估对象之间的关系多是单向性关系，评估主体主要以被评估对象所呈现的材料为主要信息源。</t>
+          <t>00355_判断题
+“书院”、“国子学”、“国子监”都是中国封建社会主要的官办高等教育机构。</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>00348_判断题
-1810年，柏林大学首先提出“通过过研究进行教学”“教学与科研统一”和“独立于自由统一”的新型教育原则。</t>
+          <t>00356_判断题
+德国高等教育系统是典型的集权管理模式。</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>00349_判断题
-欧洲中世纪大学起源于学者行会，包括教师行会和学生行会。</t>
+          <t>00357_判断题
+我国最早的学位制度可以追溯至古代的进士制度。</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -6363,21 +6331,21 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>00350_判断题
-英国高等教育具有悠久的专业教育传统。</t>
+          <t>00358_判断题
+“太学”在汉代以后又称为“国子学”、“国子监”，是中国封建社会主要的官办高等教育机构。</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>00351_判断题
-我国目前的高等教育宏观管理体制是“两级管理、分级负责、以省级为主”的体制。</t>
+          <t>00359_判断题
+发展科学的职能体现在大学的科学研究中。</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6389,8 +6357,8 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>00352_判断题
-梅贻琦任清华校长期间，极为重视教学与研究的统一。</t>
+          <t>00360_判断题
+德国大学的重心在基层讲座，大学校长是荣誉性职位。</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6402,8 +6370,8 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>00353_判断题
-高等学校课程管理主要包括课程制定者的管理、课程编制内容的管理以及课程编制活动的管理。</t>
+          <t>00361_判断题
+我国高校行使办学自主权的前提是高等学校必须坚持社会主义办学方向。</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6415,21 +6383,21 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>00354_判断题
-科学研究是高校发展的基础和支撑点。</t>
+          <t>00362_判断题
+班级授课制萌芽于15世纪末，后经德国教育家赫尔巴特总结、改进和理论提升，初步形成。</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>00355_判断题
-“书院”、“国子学”、“国子监”都是中国封建社会主要的官办高等教育机构。</t>
+          <t>00363_判断题
+高等教育评价主要研究各种高等教育现象间的关系，探索高等教育规律。</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6441,8 +6409,8 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>00356_判断题
-德国高等教育系统是典型的集权管理模式。</t>
+          <t>00364_判断题
+通才教育与专才教育之争的实质是人才的社会适应性之争。</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -6454,8 +6422,8 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>00357_判断题
-我国最早的学位制度可以追溯至古代的进士制度。</t>
+          <t>00365_判断题
+高校教学是实现一定的高等教育目的和人才培养目标的基本途径。</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6467,8 +6435,8 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>00358_判断题
-“太学”在汉代以后又称为“国子学”、“国子监”，是中国封建社会主要的官办高等教育机构。</t>
+          <t>00366_判断题
+课程在教育活动中始终处于基础和核心的地位。</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6480,47 +6448,47 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>00359_判断题
-发展科学的职能体现在大学的科学研究中。</t>
+          <t>00367_判断题
+高校教学过程的特殊性、学生学习的自主性、教师的学术自由等因素决定了高校教学管理的意义甚微。</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>00360_判断题
-德国大学的重心在基层讲座，大学校长是荣誉性职位。</t>
+          <t>00368_判断题
+教学与科研相统一的思想最早是由牛津剑桥等古典大学明确.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>00361_判断题
-我国高校行使办学自主权的前提是高等学校必须坚持社会主义办学方向。</t>
+          <t>00369_判断题
+高等学校的主体是教师、学生、学校建筑。</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>00362_判断题
-班级授课制萌芽于15世纪末，后经德国教育家赫尔巴特总结、改进和理论提升，初步形成。</t>
+          <t>00370_判断题
+当前大学政治上不够成熟，不太关注国内外大事。</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6532,8 +6500,8 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>00363_判断题
-高等教育评价主要研究各种高等教育现象间的关系，探索高等教育规律。</t>
+          <t>00371_判断题
+“雅典大学”已经初具现代意义上高等教育的组织雏形和特征。</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6545,21 +6513,21 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>00364_判断题
-通才教育与专才教育之争的实质是人才的社会适应性之争。</t>
+          <t>00372_判断题
+正确理解高等教育评价概念是进行教育评价工作的前提。</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>00365_判断题
-高校教学是实现一定的高等教育目的和人才培养目标的基本途径。</t>
+          <t>00373_判断题
+《莫里尔法案》推动了美国农工技术学院的大发展。</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6571,8 +6539,8 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>00366_判断题
-课程在教育活动中始终处于基础和核心的地位。</t>
+          <t>00374_判断题
+终结性评价是在某一相对完整的教学阶段结束后对整个教学目标实现的程度作出结论的评价。</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6584,21 +6552,21 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>00367_判断题
-高校教学过程的特殊性、学生学习的自主性、教师的学术自由等因素决定了高校教学管理的意义甚微。</t>
+          <t>00375_判断题
+美国政府极少直接干预高校的内部行为，鼓励高校展开竞争。</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>00368_判断题
-教学与科研相统一的思想最早是由牛津剑桥等古典大学明确.</t>
+          <t>00376_判断题
+专业教育通常可以依托通才教育，通识教育则通常排斥专才教育。</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6610,47 +6578,47 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>00369_判断题
-高等学校的主体是教师、学生、学校建筑。</t>
+          <t>00377_判断题
+新中国成立后，我国的高等教育目的经历了从培养“劳动者”、培养“人才”、培养“建设者和接班人”、培养“公民”的转变过程。</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>00370_判断题
-当前大学政治上不够成熟，不太关注国内外大事。</t>
+          <t>00378_判断题
+柏林大学的创立把学术研究引入大学，大学至此开始有了第二种职能——发展科学的职能。</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>00371_判断题
-“雅典大学”已经初具现代意义上高等教育的组织雏形和特征。</t>
+          <t>00379_判断题
+北美新大陆早期殖民地学院时期高等教育模式移植了英国模式。</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>00372_判断题
-正确理解高等教育评价概念是进行教育评价工作的前提。</t>
+          <t>00380_判断题
+教学永远具有教育性，科学相与思想性要相统一。</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6662,8 +6630,8 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>00373_判断题
-《莫里尔法案》推动了美国农工技术学院的大发展。</t>
+          <t>00381_判断题
+1636年建立的哈佛学院，是北美新大陆创办的第一所高等教育机构。</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6675,8 +6643,8 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>00374_判断题
-终结性评价是在某一相对完整的教学阶段结束后对整个教学目标实现的程度作出结论的评价。</t>
+          <t>00382_判断题
+高等教育是一种特殊的社会现象。</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6688,8 +6656,8 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>00375_判断题
-美国政府极少直接干预高校的内部行为，鼓励高校展开竞争。</t>
+          <t>00383_判断题
+课程管理主要在高校内部进行，在学校层面上的实施机构为教务处。</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6701,21 +6669,21 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>00376_判断题
-专业教育通常可以依托通才教育，通识教育则通常排斥专才教育。</t>
+          <t>00384_判断题
+德国大学的改革不仅影响了其他欧洲国家大学的发展，也波及大洋彼岸的美国大学。</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>00377_判断题
-新中国成立后，我国的高等教育目的经历了从培养“劳动者”、培养“人才”、培养“建设者和接班人”、培养“公民”的转变过程。</t>
+          <t>00385_判断题
+高等教育目的是教育活动的主体对客观现实之于人的素质发展的需要和可能的主观认识，以及之于人的素质发展的价值选择的统一。</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6727,21 +6695,21 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>00378_判断题
-柏林大学的创立把学术研究引入大学，大学至此开始有了第二种职能——发展科学的职能。</t>
+          <t>00386_判断题
+高等教育的萌芽阶段，一般认为在西方为欧洲中世纪时代，在中国为唐宋时代。</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>00379_判断题
-北美新大陆早期殖民地学院时期高等教育模式移植了英国模式。</t>
+          <t>00387_判断题
+高等教育的质的规定性在于高等教育是培养社会所需要的高级专门人才的一种社会活动。</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6753,8 +6721,8 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>00380_判断题
-教学永远具有教育性，科学相与思想性要相统一。</t>
+          <t>00388_判断题
+法国的大学一般由国家举办，政府对高校采取“科层化”的管理方式。</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6766,8 +6734,8 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>00381_判断题
-1636年建立的哈佛学院，是北美新大陆创办的第一所高等教育机构。</t>
+          <t>00389_判断题
+高校教学管理是行政管理与学术管理的结合。</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6779,8 +6747,8 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>00382_判断题
-高等教育是一种特殊的社会现象。</t>
+          <t>00390_判断题
+中世纪大学教育具有浓厚的宗教色彩。</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6792,8 +6760,8 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>00383_判断题
-课程管理主要在高校内部进行，在学校层面上的实施机构为教务处。</t>
+          <t>00391_判断题
+高等教育终身化使得高等教育不再是具有一定期限的人们接受教育的终结阶段。</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6805,8 +6773,8 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>00384_判断题
-德国大学的改革不仅影响了其他欧洲国家大学的发展，也波及大洋彼岸的美国大学。</t>
+          <t>00392_判断题
+教育家马卡连柯说：“要尽量多的要求一个人，也要尽可能性地尊重一个人。”</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6818,34 +6786,34 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>00385_判断题
-高等教育目的是教育活动的主体对客观现实之于人的素质发展的需要和可能的主观认识，以及之于人的素质发展的价值选择的统一。</t>
+          <t>00393_判断题
+美国高等教育系统是典型的集权管理模式。</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>00386_判断题
-高等教育的萌芽阶段，一般认为在西方为欧洲中世纪时代，在中国为唐宋时代。</t>
+          <t>00394_判断题
+我国目前的高等教育规模居于世界第一位。</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>00387_判断题
-高等教育的质的规定性在于高等教育是培养社会所需要的高级专门人才的一种社会活动。</t>
+          <t>00395_判断题
+科研是大学教师创造性最为集中的体现。</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6857,21 +6825,21 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>00388_判断题
-法国的大学一般由国家举办，政府对高校采取“科层化”的管理方式。</t>
+          <t>00396_判断题
+高等教育中所有的教学科目都可以成为学科。</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>00389_判断题
-高校教学管理是行政管理与学术管理的结合。</t>
+          <t>00397_判断题
+大学生社会实践活动是“跨世纪青年人才工程”和“跨世纪青年文明工程”的重要组成部分。</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6883,21 +6851,21 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>00390_判断题
-中世纪大学教育具有浓厚的宗教色彩。</t>
+          <t>00398_判断题
+教育方针由中央或党的最高领导人制定，每一个时期表述不同，因此无法写进法律之中。</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>00391_判断题
-高等教育终身化使得高等教育不再是具有一定期限的人们接受教育的终结阶段。</t>
+          <t>00399_判断题
+高等教育的功能最终要通过高等学校来表现，其实质就是高等学校的职能。</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6909,21 +6877,21 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>00392_判断题
-教育家马卡连柯说：“要尽量多的要求一个人，也要尽可能性地尊重一个人。”</t>
+          <t>00400_判断题
+教材是高校学科建设的核心内容，直接决定教学的成败。</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>00393_判断题
-美国高等教育系统是典型的集权管理模式。</t>
+          <t>00401_判断题
+形成性评价是在某一相对完整的教学阶段结束后对整个教学目标实现的程度作出结论的评价。</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6935,8 +6903,8 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>00394_判断题
-我国目前的高等教育规模居于世界第一位。</t>
+          <t>00402_判断题
+法国的高等教育宏观管理体制是典型的中央集权型模式。</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6948,8 +6916,8 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>00395_判断题
-科研是大学教师创造性最为集中的体现。</t>
+          <t>00403_判断题
+中世纪大学理念最突出地表现在对知识发展和对无功利学术目的的追求上。</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6961,47 +6929,47 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>00396_判断题
-高等教育中所有的教学科目都可以成为学科。</t>
+          <t>00404_判断题
+“大学自治、学术自由”的传统起源于欧洲中世纪大学。</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>00397_判断题
-大学生社会实践活动是“跨世纪青年人才工程”和“跨世纪青年文明工程”的重要组成部分。</t>
+          <t>00405_判断题
+科研是高等学校最本质最经常的活动。</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>00398_判断题
-教育方针由中央或党的最高领导人制定，每一个时期表述不同，因此无法写进法律之中。</t>
+          <t>00406_判断题
+高等教育一般包括普通高等教育、成人高等教育、高等职业教育等三种类型。</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>00399_判断题
-高等教育的功能最终要通过高等学校来表现，其实质就是高等学校的职能。</t>
+          <t>00408_判断题
+德育过程具有多开端性。</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7013,34 +6981,34 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>00400_判断题
-教材是高校学科建设的核心内容，直接决定教学的成败。</t>
+          <t>00409_判断题
+高等教育的本质就是一项巨大的事业。</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>00401_判断题
-形成性评价是在某一相对完整的教学阶段结束后对整个教学目标实现的程度作出结论的评价。</t>
+          <t>00410_判断题
+《莫里尔法案》有效促进了美国赠地学院运动的蓬勃发展。</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>00402_判断题
-法国的高等教育宏观管理体制是典型的中央集权型模式。</t>
+          <t>00411_判断题
+《中华人民共和国高等教育法》的颁布使我国高校的办学自主权自建国以来第一次得到了法律的保障。</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7052,8 +7020,8 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>00403_判断题
-中世纪大学理念最突出地表现在对知识发展和对无功利学术目的的追求上。</t>
+          <t>00412_判断题
+学习高等教育心理学有助于高校教师提高其评价反思能力。</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7065,8 +7033,8 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>00404_判断题
-“大学自治、学术自由”的传统起源于欧洲中世纪大学。</t>
+          <t>00413_判断题
+德国是首先将大学教授纳入国家公务员体系的国家。</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7078,8 +7046,8 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>00405_判断题
-科研是高等学校最本质最经常的活动。</t>
+          <t>00414_判断题
+欧洲中世纪大学在入学时间及学习年限上都有非常严格的规定。</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7091,8 +7059,8 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>00406_判断题
-高等教育一般包括普通高等教育、成人高等教育、高等职业教育等三种类型。</t>
+          <t>00415_判断题
+高校教师教学评价应以课堂教学和教学绩效评价为主。</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7104,21 +7072,21 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>00407_判断题
-选拔培养学术骨干和学科带头人是高校教师队伍建设的一项十分重要的战略任务。（该题目已移除！）</t>
+          <t>00416_判断题
+从事科研活动一般程序为科研准备阶段和科学实施阶段。</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>00408_判断题
-德育过程具有多开端性。</t>
+          <t>00417_判断题
+我国现代学位制度最早形成于民国时期。</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7130,21 +7098,21 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>00409_判断题
-高等教育的本质就是一项巨大的事业。</t>
+          <t>00418_判断题
+1776年，美国颁布《独立宣言》后，开设了大量的赠地学院。</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>00410_判断题
-《莫里尔法案》有效促进了美国赠地学院运动的蓬勃发展。</t>
+          <t>00419_判断题
+“学科”相对应的英文单词是“discipline”，意指知识的分支或教学科目。</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7156,8 +7124,8 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>00411_判断题
-《中华人民共和国高等教育法》的颁布使我国高校的办学自主权自建国以来第一次得到了法律的保障。</t>
+          <t>00420_判断题
+大学教师的基本任务是从事科研。</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7169,21 +7137,21 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>00412_判断题
-学习高等教育心理学有助于高校教师提高其评价反思能力。</t>
+          <t>00421_判断题
+区分度指的是考试结果的稳定性和可靠性程度。</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>00413_判断题
-德国是首先将大学教授纳入国家公务员体系的国家。</t>
+          <t>00422_判断题
+高等教育要促进人的发展，同样必须满足社会发展的需要。</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -7195,73 +7163,73 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>00414_判断题
-欧洲中世纪大学在入学时间及学习年限上都有非常严格的规定。</t>
+          <t>00423_判断题
+我国高校评估基本上采用的是“指标——量化”方法。</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>00415_判断题
-高校教师教学评价应以课堂教学和教学绩效评价为主。</t>
+          <t>00424_判断题
+德国大学的学术水平及质量差异极大，体现了显著的两级分化。</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>00416_判断题
-从事科研活动一般程序为科研准备阶段和科学实施阶段。</t>
+          <t>00425_判断题
+高等教育学是以高等教育的特殊矛盾与基本规律为研究对象。</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>00417_判断题
-我国现代学位制度最早形成于民国时期。</t>
+          <t>00426_判断题
+布鲁纳认为，隐性课程与显性课程同样重要。</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>00418_判断题
-1776年，美国颁布《独立宣言》后，开设了大量的赠地学院。</t>
+          <t>00427_判断题
+英国古典大学具有悠久的博雅教育传统。</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>00419_判断题
-“学科”相对应的英文单词是“discipline”，意指知识的分支或教学科目。</t>
+          <t>00428_判断题
+教学与科研相统一思想最早是由洪堡创立的德国柏林大学实现的。</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7273,21 +7241,21 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>00420_判断题
-大学教师的基本任务是从事科研。</t>
+          <t>00429_判断题
+依据马丁·特罗的划分标准，中国在本世纪初就已经进入高等教育大众化阶段。</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>00421_判断题
-区分度指的是考试结果的稳定性和可靠性程度。</t>
+          <t>00430_判断题
+课程建设应在学校的指导下，由学校教务处对全校的课程直接负责。</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7299,21 +7267,21 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>00422_判断题
-高等教育要促进人的发展，同样必须满足社会发展的需要。</t>
+          <t>00431_判断题
+教学评价是一种判断事实的活动，它用定性或定量的方法描述学生的发展水平。</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>00423_判断题
-我国高校评估基本上采用的是“指标——量化”方法。</t>
+          <t>00432_判断题
+通识教育目的是使学生在具备专业知识技能的同时具有相应的政治、文化、科学素养。</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7325,8 +7293,8 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>00424_判断题
-德国大学的学术水平及质量差异极大，体现了显著的两级分化。</t>
+          <t>00433_判断题
+本科大学生未经过系统的学术训练，不用要求他们写毕业论文。</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -7338,8 +7306,8 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>00425_判断题
-高等教育学是以高等教育的特殊矛盾与基本规律为研究对象。</t>
+          <t>00434_判断题
+教研室是各院系教学管理的基础。</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7351,8 +7319,8 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>00426_判断题
-布鲁纳认为，隐性课程与显性课程同样重要。</t>
+          <t>00435_判断题
+大学与中学有着本质的不同，因此中学的教学改革方法和模式不适合于大学借鉴。</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -7364,8 +7332,8 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>00427_判断题
-英国古典大学具有悠久的博雅教育传统。</t>
+          <t>00436_判断题
+高等教育作为一种复杂的社会领域和教育现象，它与政治、经济、文化等各个社会领域有着千丝万缕的联系，而且其自身也处于不断发展变化之中。</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7377,8 +7345,8 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>00428_判断题
-教学与科研相统一思想最早是由洪堡创立的德国柏林大学实现的。</t>
+          <t>00437_判断题
+一般认为，现代大学的直接源头为欧洲“中世纪大学”。</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -7390,21 +7358,21 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>00429_判断题
-依据马丁·特罗的划分标准，中国在本世纪初就已经进入高等教育大众化阶段。</t>
+          <t>00438_判断题
+“威斯康星思想”强调了大学主动适应社会需求，密切联系社会办学的教育理念。</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>00430_判断题
-课程建设应在学校的指导下，由学校教务处对全校的课程直接负责。</t>
+          <t>00439_判断题
+从事高等教育活动的主体是大学教师和大学生，这里的大学教师不包括高校教育管理人员。</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7416,8 +7384,8 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>00431_判断题
-教学评价是一种判断事实的活动，它用定性或定量的方法描述学生的发展水平。</t>
+          <t>00441_判断题
+校园文化主要是指各种课外活动。</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7429,8 +7397,8 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>00432_判断题
-通识教育目的是使学生在具备专业知识技能的同时具有相应的政治、文化、科学素养。</t>
+          <t>00442_判断题
+教师选择和运用教学方法时要考虑教学对象、教学目标、教学内容及自身素质等因素。</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7442,60 +7410,60 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>00433_判断题
-本科大学生未经过系统的学术训练，不用要求他们写毕业论文。</t>
+          <t>00443_判断题
+京师大学堂不是真正意义上的现代大学。</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>00434_判断题
-教研室是各院系教学管理的基础。</t>
+          <t>00444_判断题
+我国高等学校的学制结构从层次上看有专科、本科、研究生和博士四个层次。</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>00435_判断题
-大学与中学有着本质的不同，因此中学的教学改革方法和模式不适合于大学借鉴。</t>
+          <t>00445_判断题
+柏拉图和亚里斯多德在西方大学理念的形成和发展史上扮演了奠基者的角色。</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>00436_判断题
-高等教育作为一种复杂的社会领域和教育现象，它与政治、经济、文化等各个社会领域有着千丝万缕的联系，而且其自身也处于不断发展变化之中。</t>
+          <t>00446_判断题
+高等教育是提高人口数量和质量的基本手段 。</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>00437_判断题
-一般认为，现代大学的直接源头为欧洲“中世纪大学”。</t>
+          <t>00447_判断题
+素质教育是人的全面发展的重要途径和手段。</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7507,8 +7475,8 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>00438_判断题
-“威斯康星思想”强调了大学主动适应社会需求，密切联系社会办学的教育理念。</t>
+          <t>00448_判断题
+高等教育方针的有关规定表述了国家的高等教育目的。</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7520,47 +7488,47 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>00439_判断题
-从事高等教育活动的主体是大学教师和大学生，这里的大学教师不包括高校教育管理人员。</t>
+          <t>00449_判断题
+日本的高等教育办学形式结构属于典型的私立主导型。</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>00440_判断题
-依据马丁·特罗的划分标准，中国在本世纪初就已经进入高等教育大众化阶段。（该题目已移除！）</t>
+          <t>00450_判断题
+中国的学院教育出现于唐，兴盛于宋，是与太学等官学并存的私学高等教育。</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>00441_判断题
-校园文化主要是指各种课外活动。</t>
+          <t>00451_判断题
+选拔、培养学术骨干和学科带头人是高校教师队伍建设的一项十分重要的战略任务。</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>00442_判断题
-教师选择和运用教学方法时要考虑教学对象、教学目标、教学内容及自身素质等因素。</t>
+          <t>00452_判断题
+《高等教育法》规定：“高等学校自批准设立之日起取得法人资格。”</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7572,8 +7540,8 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>00443_判断题
-京师大学堂不是真正意义上的现代大学。</t>
+          <t>00453_判断题
+现代学位制度主要起源于一些西欧的中世纪大学。</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7585,34 +7553,34 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>00444_判断题
-我国高等学校的学制结构从层次上看有专科、本科、研究生和博士四个层次。</t>
+          <t>00454_判断题
+高等教育的个人本位价值观、社会本位价值观、知识本位价值观，各有其合理性和局限性，应辩证地考察。</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>00445_判断题
-柏拉图和亚里斯多德在西方大学理念的形成和发展史上扮演了奠基者的角色。</t>
+          <t>00455_判断题
+学生撰写毕业论文的选题一般由指导老师根据自己的课题研究来确定。</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>00446_判断题
-高等教育是提高人口数量和质量的基本手段 。</t>
+          <t>00456_判断题
+效度指的是考试结果的稳定性和可靠性程度，即考试结果是否真实、客观地反映了学生的实际水平。</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7624,167 +7592,37 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>00447_判断题
-素质教育是人的全面发展的重要途径和手段。</t>
+          <t>00457_判断题
+早自中国汉代的“太学”，中国高等教育机构就有了“学术自治、学术自由”的传统。</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>00448_判断题
-高等教育方针的有关规定表述了国家的高等教育目的。</t>
+          <t>00458_判断题
+美国的高等教育办学形式结构属于典型的私立主导型。</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>00449_判断题
-日本的高等教育办学形式结构属于典型的私立主导型。</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>00450_判断题
-中国的学院教育出现于唐，兴盛于宋，是与太学等官学并存的私学高等教育。</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>00451_判断题
-选拔、培养学术骨干和学科带头人是高校教师队伍建设的一项十分重要的战略任务。</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>00452_判断题
-《高等教育法》规定：“高等学校自批准设立之日起取得法人资格。”</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>00453_判断题
-现代学位制度主要起源于一些西欧的中世纪大学。</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>00454_判断题
-高等教育的个人本位价值观、社会本位价值观、知识本位价值观，各有其合理性和局限性，应辩证地考察。</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>00455_判断题
-学生撰写毕业论文的选题一般由指导老师根据自己的课题研究来确定。</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>错</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>00456_判断题
-效度指的是考试结果的稳定性和可靠性程度，即考试结果是否真实、客观地反映了学生的实际水平。</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>错</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>00457_判断题
-早自中国汉代的“太学”，中国高等教育机构就有了“学术自治、学术自由”的传统。</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>错</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>00458_判断题
-美国的高等教育办学形式结构属于典型的私立主导型。</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>错</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
           <t>00459_判断题
 人的全面发展学说是马克思主义教育的思想精髓，是当前我国教育改革和实施素质教育的理论基础。</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>对</t>
         </is>
